--- a/Roadmap/roadmap_churn_2026-2027_v2.xlsx
+++ b/Roadmap/roadmap_churn_2026-2027_v2.xlsx
@@ -883,7 +883,7 @@
       <c r="A7" s="20" t="n"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t>Environnement WSL Ubuntu + Podman opérationnel</t>
+          <t>Environnement WSL Ubuntu + Docker opérationnel</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -1427,7 +1427,7 @@
       <c r="A30" s="20" t="n"/>
       <c r="B30" s="21" t="inlineStr">
         <is>
-          <t>Pipeline ingestion Bronze→Silver (dbt · Prefect)</t>
+          <t>Pipeline ingestion Bronze→Silver (dbt · Airflow)</t>
         </is>
       </c>
       <c r="C30" s="23" t="n"/>
@@ -1663,7 +1663,7 @@
       <c r="A40" s="16" t="n"/>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>Conteneurisation Podman + docker-compose</t>
+          <t>Conteneurisation Docker + docker-compose</t>
         </is>
       </c>
       <c r="C40" s="19" t="n"/>

--- a/Roadmap/roadmap_churn_2026-2027_v2.xlsx
+++ b/Roadmap/roadmap_churn_2026-2027_v2.xlsx
@@ -1263,7 +1263,7 @@
       <c r="A23" s="16" t="n"/>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>MPD PostgreSQL Bronze/Silver/Gold + rôle MongoDB</t>
+          <t>MPD PostgreSQL Bronze/Silver/Gold + stockage JSONB des avis</t>
         </is>
       </c>
       <c r="C23" s="19" t="n"/>
@@ -1451,7 +1451,7 @@
       <c r="A31" s="16" t="n"/>
       <c r="B31" s="17" t="inlineStr">
         <is>
-          <t>Nettoyage qualité + bases Postgres / Mongo reliées</t>
+          <t>Nettoyage qualité + avis Trustpilot / SDV dans PostgreSQL (JSONB)</t>
         </is>
       </c>
       <c r="C31" s="19" t="n"/>
